--- a/output/pdf_financials_xlsx/GLDS.xlsx
+++ b/output/pdf_financials_xlsx/GLDS.xlsx
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.514781</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.841436</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.5443</v>
       </c>
     </row>
     <row r="93">
@@ -2361,13 +2361,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.4925</v>
+        <v>-0.039125</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.287008</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.642607</v>
       </c>
     </row>
     <row r="119">
@@ -3000,7 +3000,11 @@
           <t>Reserves (note 9)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>1.514781</v>
       </c>
@@ -3335,7 +3339,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>-0.531625</v>
       </c>

--- a/output/pdf_financials_xlsx/GLDS.xlsx
+++ b/output/pdf_financials_xlsx/GLDS.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.015873</v>
       </c>
     </row>
     <row r="13">
@@ -869,7 +869,7 @@
         <v>-0.819558</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.436851</v>
+        <v>-0.452724</v>
       </c>
     </row>
     <row r="28">
@@ -901,7 +901,7 @@
         <v>-0.819558</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.436851</v>
+        <v>-0.452724</v>
       </c>
     </row>
     <row r="30">
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.168393</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.265349</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.538698</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.168393</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.265349</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.538698</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.177045</v>
+        <v>0.008652</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.357462</v>
+        <v>0.092113</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.549256</v>
+        <v>0.010558</v>
       </c>
     </row>
     <row r="49">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">

--- a/output/pdf_financials_xlsx/GLDS.xlsx
+++ b/output/pdf_financials_xlsx/GLDS.xlsx
@@ -3401,7 +3401,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
